--- a/02table/TableS5_Gene_Ontology_for_modules.xlsx
+++ b/02table/TableS5_Gene_Ontology_for_modules.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11113"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047068B9-27CD-CA40-8F08-62994E224403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD196628-B99A-DD4A-9B28-4D25BE39D46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34620" yWindow="2080" windowWidth="30240" windowHeight="16620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8304,7 +8304,7 @@
     </r>
   </si>
   <si>
-    <t>Table S5 Gene Ontology enrichment analysis was performed using the genes in each module of the co-expression network constructed from the hybrid population.</t>
+    <t>Table S5. Gene Ontology enrichment analysis was performed using the genes in each module of the co-expression network constructed from the hybrid population.</t>
   </si>
 </sst>
 </file>
